--- a/サキュレ_得意先コード統一マスター.xlsx
+++ b/サキュレ_得意先コード統一マスター.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,14 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="001A6B2E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +97,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -154,6 +170,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,928 +610,928 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>MT-001</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>新宿線新宿三丁目駅</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>MT-002</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>新宿線曙橋駅</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>MT-003</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>新宿線市ヶ谷駅</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>MT-004</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>新宿線神保町駅</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>MT-005</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>三田線神保町駅</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>MT-006</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>新宿線小川町駅</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>MT-007</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>新宿線九段下駅</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>MT-008</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>新宿線岩本町駅</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>MT-009</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>浅草線人形町駅</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>MT-010</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>新宿線馬喰横山駅</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>MT-011</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>浅草線東日本橋駅</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>MT-012</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>浅草線浅草橋駅</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>MT-013</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>大江戸線蔵前駅</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>MT-014</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>浅草線浅草駅</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>MT-015</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>浅草線蔵前駅</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>MT-016</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>新宿線森下駅</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>MT-017</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>大江戸線森下駅</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>MT-018</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>新宿線菊川駅</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>MT-019</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>新宿線住吉駅</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>MT-020</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>新宿線西大島駅</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>MT-021</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>新宿線大島駅</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>MT-022</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>新宿線東大島駅</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>MT-023</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>大島乗務区（都交通局）</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>MT-024</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>新宿線船堀駅</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>MT-025</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>新宿線一之江駅</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>MT-026</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>新宿線瑞江駅</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>MT-027</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>新宿線篠崎駅</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>MT-028</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>新宿線浜町駅</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -1536,103 +1567,103 @@
       <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>MT-029</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>大江戸線飯田橋駅</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr"/>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>MT-030</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>大江戸線若松河田駅</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>MT-031</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>大江戸線東新宿駅</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -1767,70 +1798,70 @@
       <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>MT-032</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>大江戸線新宿西口駅</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>MT-033</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>大江戸線都庁前駅</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -1899,37 +1930,37 @@
       <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>MT-034</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>大江戸線中野坂上駅</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -1965,598 +1996,598 @@
       <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>MT-035</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>大江戸線中井駅</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>MT-036</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>大江戸線落合南長崎駅</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr"/>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>MT-037</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>大江戸線練馬駅</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>MT-038</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>大江戸線豊島園駅</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>MT-039</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>大江戸線練馬春日町駅</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>MT-040</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>大江戸線光が丘駅</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr"/>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>MT-041</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>光が丘乗務区（都交通局）</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr"/>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>MT-042</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>三田線西高島平駅</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr"/>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>MT-043</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>三田線新高島平駅</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr"/>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>MT-044</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>三田線高島平駅</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr"/>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>MT-045</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>三田線西台駅</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr"/>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>MT-046</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>三田線蓮根駅</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr"/>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>MT-047</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>大江戸線牛込神楽坂駅</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>MT-048</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>大江戸線牛込柳町駅</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr"/>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>MT-049</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>大江戸線西新宿五丁目駅</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>MT-050</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>大江戸線東中野駅</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr"/>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>MT-051</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>大江戸線新江古田駅</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>MT-052</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>三田線志村三丁目</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>大迫</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr"/>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
@@ -2625,433 +2656,433 @@
       <c r="G64" s="7" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>MT-053</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>大江戸線新宿駅</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr"/>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>MT-054</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>大江戸線青山一丁目駅</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr"/>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>MT-055</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>大江戸線六本木駅</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr"/>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>MT-056</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>大江戸線赤羽橋駅</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr"/>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>MT-057</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>浅草線泉岳寺駅</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr"/>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>MT-058</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>浅草線三田駅</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr"/>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>MT-059</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>三田線三田駅</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr"/>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>MT-060</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>三田線芝公園駅</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr"/>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>MT-061</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>大江戸線大門駅</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr"/>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>MT-062</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>大江戸線築地市場駅</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr"/>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>MT-063</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>大江戸線勝どき駅</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr"/>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>MT-064</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>大江戸線月島駅</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr"/>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>MT-065</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>大江戸線門前仲町駅</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -3087,136 +3118,136 @@
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>MT-066</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>大江戸線両国駅</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr"/>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>MT-067</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>浅草線本所吾妻橋駅</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr"/>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>MT-068</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>日暮里舎人ライナー日暮里駅</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr"/>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>MT-069</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>日暮里舎人ライナー西日暮里駅</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr"/>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -3285,37 +3316,37 @@
       <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>MT-070</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>荒川電車営業所</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr"/>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -3351,37 +3382,37 @@
       <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>MT-071</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>大江戸線代々木駅</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr"/>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -3417,169 +3448,169 @@
       <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>MT-072</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>大江戸線国立競技場</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>MT-073</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>大江戸線汐留駅</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr"/>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>MT-074</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>大江戸線清澄白河駅</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr"/>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>MT-075</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>日暮里舎人ライナー舎人駅</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>MT-076</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>大江戸線麻布十番駅</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
         <is>
           <t>岡田</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr"/>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
@@ -3615,1126 +3646,1126 @@
       <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>MT-077</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>浅草線日本橋駅</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr"/>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>MT-078</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>都営新宿線本八幡駅</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr"/>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>MT-079</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>浅草線高輪台駅</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>MT-080</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>浅草線五反田駅</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr"/>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>MT-081</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
         <is>
           <t>浅草線戸越駅</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr"/>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>MT-082</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>旧西馬込乗務区庁舎（都交通局）</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>MT-083</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>浅草線西馬込駅</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr"/>
+      <c r="F101" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>MT-084</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>浅草線馬込駅</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr"/>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>MT-085</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>浅草線中延駅</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>MT-086</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
         <is>
           <t>三田線御成門駅</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr"/>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>MT-087</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>浅草線新橋駅</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>MT-088</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
         <is>
           <t>荒川電車営業所（都交通局）</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
         <is>
           <t>宮原</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>MT-089</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
         <is>
           <t>大江戸線上野御徒町駅</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>MT-090</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t>大江戸線新御徒町駅</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>MT-091</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
         <is>
           <t>三田線大手町駅</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="F109" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>MT-092</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
         <is>
           <t>三田線日比谷駅</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr"/>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>MT-093</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>三田線内幸町駅</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="F111" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>MT-094</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>浅草線東銀座駅</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="inlineStr"/>
+      <c r="F112" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>MT-095</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>浅草線宝町駅</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
         <is>
           <t>宮原・玉山</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>MT-096</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>三田線春日駅</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr"/>
+      <c r="F114" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>MT-097</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
         <is>
           <t>大江戸線春日駅</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>MT-098</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
         <is>
           <t>三田線水道橋駅</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr"/>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>MT-099</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
         <is>
           <t>大江戸線本郷三丁目駅</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr"/>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>MT-100</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
         <is>
           <t>三田線白山駅</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr"/>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="A119" s="13" t="inlineStr">
+        <is>
+          <t>MT-101</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
         <is>
           <t>三田線千石駅</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr"/>
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>MT-102</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
         <is>
           <t>三田線巣鴨駅</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr"/>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="A121" s="13" t="inlineStr">
+        <is>
+          <t>MT-103</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>三田線西巣鴨駅</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr"/>
+      <c r="F121" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>MT-104</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
         <is>
           <t>三田線新板橋駅</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr"/>
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>MT-105</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
         <is>
           <t>三田線板橋区役所前駅</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G123" s="4" t="inlineStr"/>
+      <c r="F123" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>MT-106</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
         <is>
           <t>三田線板橋本町駅</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr"/>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>MT-107</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
         <is>
           <t>三田線本蓮沼駅</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr"/>
+      <c r="F125" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>MT-108</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
         <is>
           <t>三田線志村坂下駅</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr"/>
+      <c r="F126" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>MT-109</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
         <is>
           <t>三田線志村三丁目駅</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr"/>
+      <c r="F127" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>MT-???</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>MT-110</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>日暮里・舎人ライナー舎人駅</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>都営地下鉄</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>都営地下鉄</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
         <is>
           <t>渡辺・柳沼</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>新規（要確認）</t>
-        </is>
-      </c>
-      <c r="G128" s="4" t="inlineStr"/>
+      <c r="F128" s="16" t="inlineStr">
+        <is>
+          <t>新規付番済</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
@@ -16518,10 +16549,11 @@
       </c>
       <c r="G502" s="7" t="inlineStr"/>
     </row>
+    <row r="503"/>
     <row r="504">
-      <c r="A504" s="12" t="inlineStr">
-        <is>
-          <t>【凡例】 白/色付き=拠点マスターと突合済み　黄色=新規登録（要確認）  TK-???/MT-???=東急・都営で拠点マスター未登録</t>
+      <c r="A504" s="17" t="inlineStr">
+        <is>
+          <t>MT-111</t>
         </is>
       </c>
     </row>
